--- a/sources/king_step8.xlsx
+++ b/sources/king_step8.xlsx
@@ -1417,11 +1417,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1484,11 +1479,6 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1551,11 +1541,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1616,11 +1601,6 @@
       <c r="U17" t="inlineStr">
         <is>
           <t>1+2</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">

--- a/sources/king_step8.xlsx
+++ b/sources/king_step8.xlsx
@@ -10408,12 +10408,12 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">

--- a/sources/king_step8.xlsx
+++ b/sources/king_step8.xlsx
@@ -1417,6 +1417,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1479,6 +1484,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1541,6 +1551,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1603,6 +1618,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1670,6 +1690,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1722,6 +1747,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1779,6 +1809,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1836,6 +1871,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1893,6 +1933,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1950,6 +1995,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -2007,6 +2057,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -2064,6 +2119,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -2121,6 +2181,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -2178,6 +2243,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -2245,6 +2315,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -2297,6 +2372,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -2354,6 +2434,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -2421,6 +2506,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -2483,6 +2573,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -2545,6 +2640,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -2602,6 +2702,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -2657,6 +2762,11 @@
       <c r="U35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -2871,6 +2981,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -2933,6 +3048,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -2990,6 +3110,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -3047,6 +3172,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -3104,6 +3234,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -3166,6 +3301,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="Z44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -3228,6 +3368,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="Z45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -3290,6 +3435,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="Z46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -3352,6 +3502,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -3412,6 +3567,11 @@
       <c r="U48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -10628,6 +10788,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="Z132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -10680,6 +10845,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="Z133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -10737,6 +10907,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="Z134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -10794,6 +10969,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="Z135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -10851,6 +11031,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="Z136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -10918,6 +11103,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="Z137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -10975,6 +11165,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="Z138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -11032,6 +11227,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="Z139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -11094,6 +11294,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="Z140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -11146,6 +11351,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="Z141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -11203,6 +11413,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="Z142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -11260,6 +11475,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="Z143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -11317,6 +11537,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="Z144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -11374,6 +11599,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="Z145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -11431,6 +11661,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="Z146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -11503,6 +11738,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="Z147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -11560,6 +11800,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="Z148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -11617,6 +11862,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -11674,6 +11924,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="Z150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -11731,6 +11986,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="Z151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -11788,6 +12048,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="Z152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -11845,6 +12110,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="Z153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -11902,6 +12172,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="Z154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -11959,6 +12234,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="Z155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -12016,6 +12296,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="Z156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -12073,6 +12358,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="Z157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -12130,6 +12420,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="Z158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -12187,6 +12482,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="Z159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -12244,6 +12544,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="Z160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -12306,6 +12611,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="Z161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -12368,6 +12678,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="Z162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -12425,6 +12740,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="Z163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -12477,6 +12797,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="Z164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -12534,6 +12859,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="Z165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -12591,6 +12921,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="Z166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -12648,6 +12983,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="Z167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -12705,6 +13045,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="Z168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -12762,6 +13107,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="Z169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -12819,6 +13169,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="Z170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -12874,6 +13229,11 @@
       <c r="U171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
@@ -13078,6 +13438,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="Z175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -13125,6 +13490,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="Z176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -13172,6 +13542,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="Z177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -13219,6 +13594,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="Z178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -13266,6 +13646,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="Z179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -13313,6 +13698,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="Z180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -13360,6 +13750,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="Z181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -13407,6 +13802,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="Z182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -13454,6 +13854,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="Z183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -13499,6 +13904,11 @@
       <c r="S184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
